--- a/00_REFERENCE_INTAKE/ssi/Large Test File Leveled Critical - Secondary - Teritiary - with driving slack to UID_152_Directional_Path_Analysis_2026-7-14-17-22-42.xlsx
+++ b/00_REFERENCE_INTAKE/ssi/Large Test File Leveled Critical - Secondary - Teritiary - with driving slack to UID_152_Directional_Path_Analysis_2026-7-14-17-22-42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpolitte\Desktop\.mpp test files\Reference Files\.mpp test files\Large Test File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{948356B1-6F6D-41B5-9119-042D13CAB82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72C2D2C4-8CDE-499C-8B40-370495D074DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,7 +563,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5BCD2D6D-5EEB-45F7-83A2-8AAEF1A81A2D}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CA2EAE19-BA8E-423E-92F6-30C9566FD3A5}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
